--- a/downloads/uttarakhand.xlsx
+++ b/downloads/uttarakhand.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Every Uttarakhand constituency, with names added and removed after the draft by sex</t>
+          <t>Every Uttarakhand constituency, with names added and deleted after the draft by sex</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Objections admitted after the draft (Form 7 and transfers out on Form 8), which are the names removed after the draft, as a count.</t>
+          <t>Objections admitted after the draft (Form 7 and transfers out on Form 8), which are the names deleted after the draft, as a count.</t>
         </is>
       </c>
     </row>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Objections admitted after the draft, which are the names removed after the draft, as a count.</t>
+          <t>Objections admitted after the draft, which are the names deleted after the draft, as a count.</t>
         </is>
       </c>
     </row>
